--- a/data/links.xlsx
+++ b/data/links.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Geteilte Ablagen\KEKS- Kores\Code\Pypsa proto\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Keks-repo\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37C1BFE8-2FD5-4640-91B0-1AF69A75EDE4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9702C24C-C146-4386-BC39-6702460EBCB9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -529,7 +529,7 @@
         <v>0.95</v>
       </c>
       <c r="G3" s="1">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="I3">
         <v>-1</v>
@@ -552,7 +552,7 @@
         <v>0.95</v>
       </c>
       <c r="G4" s="1">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -575,7 +575,7 @@
         <v>0.95</v>
       </c>
       <c r="G5" s="1">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="I5">
         <v>-1</v>

--- a/data/links.xlsx
+++ b/data/links.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Keks-repo\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Keks-repo\KEKS\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9702C24C-C146-4386-BC39-6702460EBCB9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BC285FB-4AAA-4670-9A94-79F5D7E17779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3015" yWindow="1590" windowWidth="21600" windowHeight="13185" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="58">
   <si>
     <t>name</t>
   </si>
@@ -102,24 +102,15 @@
     <t>Industry_boiler</t>
   </si>
   <si>
-    <t>Industry_1_thermal</t>
-  </si>
-  <si>
     <t>Kritis_CHP</t>
   </si>
   <si>
-    <t>Kritis_1_thermal</t>
-  </si>
-  <si>
     <t>efficiency2</t>
   </si>
   <si>
     <t>Residential_HeatPump</t>
   </si>
   <si>
-    <t>Residential_1_thermal</t>
-  </si>
-  <si>
     <t>HP</t>
   </si>
   <si>
@@ -130,6 +121,84 @@
   </si>
   <si>
     <t>marginal_cost</t>
+  </si>
+  <si>
+    <t>Residential2</t>
+  </si>
+  <si>
+    <t>Residential3</t>
+  </si>
+  <si>
+    <t>Residential_2</t>
+  </si>
+  <si>
+    <t>Residential_3</t>
+  </si>
+  <si>
+    <t>DHN_res2</t>
+  </si>
+  <si>
+    <t>DEP_1</t>
+  </si>
+  <si>
+    <t>DHN_res3</t>
+  </si>
+  <si>
+    <t>AC</t>
+  </si>
+  <si>
+    <t>thermal</t>
+  </si>
+  <si>
+    <t>gas</t>
+  </si>
+  <si>
+    <t>Gas_to_DEP</t>
+  </si>
+  <si>
+    <t>DEP_1_gas</t>
+  </si>
+  <si>
+    <t>DEP</t>
+  </si>
+  <si>
+    <t>DEP_CHP</t>
+  </si>
+  <si>
+    <t>DEP_HP</t>
+  </si>
+  <si>
+    <t>DEP_1_LT</t>
+  </si>
+  <si>
+    <t>Residential_2_LT</t>
+  </si>
+  <si>
+    <t>Residential_3_LT</t>
+  </si>
+  <si>
+    <t>DEP_1_HT</t>
+  </si>
+  <si>
+    <t>Residential_2_HT</t>
+  </si>
+  <si>
+    <t>Residential_3_HT</t>
+  </si>
+  <si>
+    <t>Exergy_red1</t>
+  </si>
+  <si>
+    <t>Exergy_red2</t>
+  </si>
+  <si>
+    <t>Industry_1_HT</t>
+  </si>
+  <si>
+    <t>Kritis_1_HT</t>
+  </si>
+  <si>
+    <t>Residential_1_HT</t>
   </si>
 </sst>
 </file>
@@ -165,8 +234,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -448,15 +516,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" customWidth="1"/>
     <col min="5" max="5" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -470,14 +538,14 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>15</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>28</v>
+      <c r="F1" t="s">
+        <v>26</v>
       </c>
       <c r="G1" t="s">
         <v>4</v>
@@ -489,7 +557,7 @@
         <v>16</v>
       </c>
       <c r="J1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -508,6 +576,9 @@
       <c r="G2">
         <v>100</v>
       </c>
+      <c r="H2" t="s">
+        <v>39</v>
+      </c>
       <c r="I2">
         <v>-1</v>
       </c>
@@ -519,17 +590,20 @@
       <c r="A3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3">
         <v>0.95</v>
       </c>
-      <c r="G3" s="1">
-        <v>1</v>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3" t="s">
+        <v>39</v>
       </c>
       <c r="I3">
         <v>-1</v>
@@ -542,17 +616,20 @@
       <c r="A4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4">
         <v>0.95</v>
       </c>
-      <c r="G4" s="1">
-        <v>1</v>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4" t="s">
+        <v>39</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -565,17 +642,20 @@
       <c r="A5" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5">
         <v>0.95</v>
       </c>
-      <c r="G5" s="1">
-        <v>1</v>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5" t="s">
+        <v>39</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -586,19 +666,25 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E6">
-        <v>0.99</v>
+        <v>0.95</v>
       </c>
       <c r="G6">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="H6" t="s">
+        <v>39</v>
+      </c>
+      <c r="I6">
+        <v>-1</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -606,19 +692,25 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
+      </c>
+      <c r="B7" t="s">
+        <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" s="1">
-        <v>0.99</v>
-      </c>
-      <c r="G7" s="1">
-        <v>100</v>
+        <v>35</v>
+      </c>
+      <c r="E7">
+        <v>0.95</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I7">
+        <v>-1</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -626,19 +718,25 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>23</v>
+        <v>44</v>
+      </c>
+      <c r="B8" t="s">
+        <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="1">
-        <v>0.99</v>
-      </c>
-      <c r="G8" s="1">
-        <v>100</v>
+        <v>37</v>
+      </c>
+      <c r="E8">
+        <v>0.95</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8" t="s">
+        <v>39</v>
+      </c>
+      <c r="I8">
+        <v>-1</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -646,73 +744,331 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="E9">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G9">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H9" t="s">
-        <v>33</v>
-      </c>
-      <c r="J9">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="E10">
-        <v>0.6</v>
-      </c>
-      <c r="F10" s="1">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="G10">
         <v>1</v>
       </c>
       <c r="H10" t="s">
-        <v>32</v>
-      </c>
-      <c r="J10">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11">
+        <v>0.8</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12">
+        <v>0.8</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E13">
+        <v>0.8</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" t="s">
+        <v>49</v>
+      </c>
+      <c r="E14">
+        <v>0.8</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15">
+        <v>0.99</v>
+      </c>
+      <c r="G15">
+        <v>100</v>
+      </c>
+      <c r="H15" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16">
+        <v>0.99</v>
+      </c>
+      <c r="G16">
+        <v>100</v>
+      </c>
+      <c r="H16" t="s">
+        <v>41</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17">
+        <v>0.99</v>
+      </c>
+      <c r="G17">
+        <v>100</v>
+      </c>
+      <c r="H17" t="s">
+        <v>41</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18">
+        <v>0.99</v>
+      </c>
+      <c r="G18">
+        <v>100</v>
+      </c>
+      <c r="H18" t="s">
+        <v>41</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" t="s">
+        <v>55</v>
+      </c>
+      <c r="E19">
+        <v>0.9</v>
+      </c>
+      <c r="G19">
+        <v>0.5</v>
+      </c>
+      <c r="H19" t="s">
+        <v>30</v>
+      </c>
+      <c r="J19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E20">
+        <v>0.6</v>
+      </c>
+      <c r="F20">
+        <v>0.3</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20" t="s">
         <v>29</v>
       </c>
-      <c r="B11" t="s">
+      <c r="J20">
         <v>10</v>
       </c>
-      <c r="C11" t="s">
-        <v>30</v>
-      </c>
-      <c r="G11">
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" t="s">
+        <v>57</v>
+      </c>
+      <c r="G21">
         <v>0.5</v>
       </c>
-      <c r="H11" t="s">
-        <v>31</v>
-      </c>
-      <c r="J11">
+      <c r="H21" t="s">
+        <v>28</v>
+      </c>
+      <c r="J21">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" t="s">
+        <v>50</v>
+      </c>
+      <c r="D22" t="s">
+        <v>37</v>
+      </c>
+      <c r="E22">
+        <v>0.6</v>
+      </c>
+      <c r="F22">
+        <v>0.3</v>
+      </c>
+      <c r="G22">
+        <v>0.25</v>
+      </c>
+      <c r="H22" t="s">
+        <v>29</v>
+      </c>
+      <c r="J22">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>46</v>
+      </c>
+      <c r="B23" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" t="s">
+        <v>47</v>
+      </c>
+      <c r="G23">
+        <v>0.5</v>
+      </c>
+      <c r="H23" t="s">
+        <v>28</v>
+      </c>
+      <c r="J23">
         <v>8</v>
       </c>
     </row>

--- a/data/links.xlsx
+++ b/data/links.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Keks-repo\KEKS\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Keks-repo\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BC285FB-4AAA-4670-9A94-79F5D7E17779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8EF77CB-DF02-4BD1-9585-542B49E040F8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3015" yWindow="1590" windowWidth="21600" windowHeight="13185" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="58">
   <si>
     <t>name</t>
   </si>
@@ -135,21 +135,12 @@
     <t>Residential_3</t>
   </si>
   <si>
-    <t>DHN_res2</t>
-  </si>
-  <si>
     <t>DEP_1</t>
   </si>
   <si>
-    <t>DHN_res3</t>
-  </si>
-  <si>
     <t>AC</t>
   </si>
   <si>
-    <t>thermal</t>
-  </si>
-  <si>
     <t>gas</t>
   </si>
   <si>
@@ -186,12 +177,6 @@
     <t>Residential_3_HT</t>
   </si>
   <si>
-    <t>Exergy_red1</t>
-  </si>
-  <si>
-    <t>Exergy_red2</t>
-  </si>
-  <si>
     <t>Industry_1_HT</t>
   </si>
   <si>
@@ -199,6 +184,21 @@
   </si>
   <si>
     <t>Residential_1_HT</t>
+  </si>
+  <si>
+    <t>DHN_res2_LT</t>
+  </si>
+  <si>
+    <t>DHN_res3_LT</t>
+  </si>
+  <si>
+    <t>DHN_res2_HT</t>
+  </si>
+  <si>
+    <t>DHN_res3_HT</t>
+  </si>
+  <si>
+    <t>DHN</t>
   </si>
 </sst>
 </file>
@@ -516,11 +516,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.140625" customWidth="1"/>
     <col min="5" max="5" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -577,7 +577,7 @@
         <v>100</v>
       </c>
       <c r="H2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I2">
         <v>-1</v>
@@ -603,7 +603,7 @@
         <v>1</v>
       </c>
       <c r="H3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I3">
         <v>-1</v>
@@ -629,7 +629,7 @@
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -655,7 +655,7 @@
         <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -681,7 +681,7 @@
         <v>1</v>
       </c>
       <c r="H6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -707,7 +707,7 @@
         <v>1</v>
       </c>
       <c r="H7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I7">
         <v>-1</v>
@@ -718,13 +718,13 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B8" t="s">
         <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E8">
         <v>0.95</v>
@@ -733,7 +733,7 @@
         <v>1</v>
       </c>
       <c r="H8" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I8">
         <v>-1</v>
@@ -744,13 +744,13 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="B9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E9">
         <v>0.8</v>
@@ -759,18 +759,18 @@
         <v>1</v>
       </c>
       <c r="H9" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="B10" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E10">
         <v>0.8</v>
@@ -779,18 +779,18 @@
         <v>1</v>
       </c>
       <c r="H10" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="B11" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E11">
         <v>0.8</v>
@@ -799,18 +799,18 @@
         <v>1</v>
       </c>
       <c r="H11" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="B12" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E12">
         <v>0.8</v>
@@ -819,58 +819,61 @@
         <v>1</v>
       </c>
       <c r="H12" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E13">
-        <v>0.8</v>
+        <v>0.99</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="E14">
-        <v>0.8</v>
+        <v>0.99</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H14" t="s">
-        <v>40</v>
+        <v>38</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="B15" t="s">
         <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="E15">
         <v>0.99</v>
@@ -879,18 +882,21 @@
         <v>100</v>
       </c>
       <c r="H15" t="s">
-        <v>41</v>
+        <v>38</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B16" t="s">
         <v>23</v>
       </c>
       <c r="C16" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E16">
         <v>0.99</v>
@@ -899,7 +905,7 @@
         <v>100</v>
       </c>
       <c r="H16" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -907,85 +913,88 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C17" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E17">
-        <v>0.99</v>
+        <v>0.9</v>
       </c>
       <c r="G17">
-        <v>100</v>
+        <v>0.5</v>
       </c>
       <c r="H17" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C18" t="s">
-        <v>22</v>
+        <v>51</v>
+      </c>
+      <c r="D18" t="s">
+        <v>9</v>
       </c>
       <c r="E18">
-        <v>0.99</v>
+        <v>0.6</v>
+      </c>
+      <c r="F18">
+        <v>0.3</v>
       </c>
       <c r="G18">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="H18" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B19" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C19" t="s">
-        <v>55</v>
-      </c>
-      <c r="E19">
-        <v>0.9</v>
+        <v>52</v>
       </c>
       <c r="G19">
         <v>0.5</v>
       </c>
       <c r="H19" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J19">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C20" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="D20" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="E20">
         <v>0.6</v>
@@ -994,7 +1003,7 @@
         <v>0.3</v>
       </c>
       <c r="G20">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="H20" t="s">
         <v>29</v>
@@ -1005,13 +1014,13 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="B21" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="C21" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="G21">
         <v>0.5</v>
@@ -1020,55 +1029,6 @@
         <v>28</v>
       </c>
       <c r="J21">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>45</v>
-      </c>
-      <c r="B22" t="s">
-        <v>43</v>
-      </c>
-      <c r="C22" t="s">
-        <v>50</v>
-      </c>
-      <c r="D22" t="s">
-        <v>37</v>
-      </c>
-      <c r="E22">
-        <v>0.6</v>
-      </c>
-      <c r="F22">
-        <v>0.3</v>
-      </c>
-      <c r="G22">
-        <v>0.25</v>
-      </c>
-      <c r="H22" t="s">
-        <v>29</v>
-      </c>
-      <c r="J22">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>46</v>
-      </c>
-      <c r="B23" t="s">
-        <v>37</v>
-      </c>
-      <c r="C23" t="s">
-        <v>47</v>
-      </c>
-      <c r="G23">
-        <v>0.5</v>
-      </c>
-      <c r="H23" t="s">
-        <v>28</v>
-      </c>
-      <c r="J23">
         <v>8</v>
       </c>
     </row>
